--- a/cms-server/utils/clModel.xlsx
+++ b/cms-server/utils/clModel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13800"/>
+    <workbookView windowHeight="14980"/>
   </bookViews>
   <sheets>
     <sheet name="a" sheetId="1" r:id="rId1"/>
@@ -14,9 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20">
-  <si>
-    <t>加工项目BOM表---</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+  <si>
+    <t>备料清单---</t>
+  </si>
+  <si>
+    <t>编号：JL-8s5-03</t>
   </si>
   <si>
     <t>客户编号</t>
@@ -79,7 +82,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -119,26 +122,57 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="DengXian"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="DengXian"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="DengXian"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -150,6 +184,81 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="DengXian"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="DengXian"/>
@@ -157,114 +266,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,13 +288,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -303,19 +366,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -325,152 +472,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="21">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -485,21 +488,23 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
       <top/>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="8"/>
       </left>
       <right/>
@@ -510,23 +515,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="8"/>
       </left>
       <right/>
       <top style="thin">
-        <color auto="1"/>
+        <color indexed="8"/>
       </top>
       <bottom style="thin">
         <color indexed="8"/>
@@ -537,46 +531,105 @@
       <left/>
       <right style="thin">
         <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="8"/>
       </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
       <right style="thin">
         <color indexed="8"/>
       </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="8"/>
       </top>
@@ -606,21 +659,52 @@
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="8"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="8"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="8"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -649,39 +733,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -697,17 +748,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -722,187 +762,216 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -917,84 +986,102 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
   <extLst>
@@ -1261,10 +1348,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.83035714285714" defaultRowHeight="12"/>
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr defaultColWidth="8.83035714285714" defaultRowHeight="15.2"/>
   <cols>
     <col min="1" max="1" width="4.61607142857143" customWidth="1"/>
     <col min="2" max="2" width="24.5535714285714" customWidth="1"/>
@@ -1275,132 +1362,137 @@
     <col min="7" max="7" width="9.66964285714286" customWidth="1"/>
     <col min="8" max="8" width="11.1607142857143" customWidth="1"/>
     <col min="9" max="9" width="12.3303571428571" customWidth="1"/>
+    <col min="10" max="10" width="15.3214285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="33" customHeight="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" ht="33" customHeight="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="22"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="32"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="19" customHeight="1" spans="1:10">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="19" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="23"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="19" customHeight="1" spans="1:10">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="25"/>
+      <c r="H3" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="22"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="20" customHeight="1" spans="1:10">
-      <c r="A4" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="21" t="s">
+      <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="22"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="25"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="21" customHeight="1" spans="1:10">
-      <c r="A5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="21" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="22"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="29"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="21" customHeight="1" spans="1:10">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="22"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
     </row>
-    <row r="7" ht="31" customHeight="1" spans="1:9">
-      <c r="A7" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="15" t="s">
+    <row r="7" ht="31" customHeight="1" spans="1:10">
+      <c r="A7" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="B7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="C7" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="D7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="E7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="F7" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="G7" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="H7" s="30" t="s">
         <v>19</v>
       </c>
+      <c r="I7" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="33"/>
     </row>
     <row r="8" ht="21" customHeight="1"/>
     <row r="9" ht="21" customHeight="1"/>
@@ -1423,25 +1515,26 @@
     <row r="26" ht="21" customHeight="1"/>
     <row r="27" ht="21" customHeight="1"/>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H2:J2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H3:J3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H4:J4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="I7:J7"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
